--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\NC\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/NC/trans/VSbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9F8D38E-4505-4642-A3DF-07A60CF541E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07E2BAD2-9210-BD45-949D-DA1A84031847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1629,9 +1628,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1642,7 +1641,7 @@
         <v>25</v>
       </c>
       <c r="C1" s="104">
-        <v>45258</v>
+        <v>45295</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1755,14 +1754,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr defaultRowHeight="8.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="14">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1800,7 +1799,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="9">
+    <row r="3" spans="1:16" ht="11">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1842,7 +1841,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="9">
+    <row r="5" spans="1:16" ht="11">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1870,7 +1869,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="9">
+    <row r="6" spans="1:16" ht="11">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1898,7 +1897,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="9">
+    <row r="7" spans="1:16" ht="11">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1944,7 +1943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="9">
+    <row r="8" spans="1:16" ht="11">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1992,7 +1991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="9">
+    <row r="9" spans="1:16" ht="11">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2032,7 +2031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="9">
+    <row r="10" spans="1:16" ht="11">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="9">
+    <row r="11" spans="1:16" ht="11">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="9">
+    <row r="12" spans="1:16" ht="11">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="9">
+    <row r="13" spans="1:16" ht="11">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="9">
+    <row r="14" spans="1:16" ht="11">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2282,7 +2281,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="9">
+    <row r="15" spans="1:16" ht="11">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9">
+    <row r="16" spans="1:16" ht="11">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2382,7 +2381,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9">
+    <row r="17" spans="1:16" ht="11">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9">
+    <row r="18" spans="1:16" ht="11">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9">
+    <row r="19" spans="1:16" ht="11">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9">
+    <row r="20" spans="1:16" ht="11">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9">
+    <row r="21" spans="1:16" ht="11">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9">
+    <row r="22" spans="1:16" ht="11">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2682,7 +2681,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9">
+    <row r="23" spans="1:16" ht="11">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9">
+    <row r="24" spans="1:16" ht="11">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9">
+    <row r="25" spans="1:16" ht="11">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2832,7 +2831,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9">
+    <row r="26" spans="1:16" ht="11">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2882,7 +2881,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="9">
+    <row r="27" spans="1:16" ht="11">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2932,7 +2931,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9">
+    <row r="28" spans="1:16" ht="11">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2982,7 +2981,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9">
+    <row r="29" spans="1:16" ht="11">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9">
+    <row r="30" spans="1:16" ht="11">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3082,7 +3081,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9">
+    <row r="31" spans="1:16" ht="11">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9">
+    <row r="32" spans="1:16" ht="11">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="9">
+    <row r="33" spans="1:16" ht="11">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="9">
+    <row r="34" spans="1:16" ht="11">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3282,7 +3281,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="9">
+    <row r="35" spans="1:16" ht="11">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3332,7 +3331,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="9">
+    <row r="36" spans="1:16" ht="11">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="9">
+    <row r="37" spans="1:16" ht="11">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3432,7 +3431,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="9">
+    <row r="38" spans="1:16" ht="11">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="9">
+    <row r="39" spans="1:16" ht="11">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="9">
+    <row r="40" spans="1:16" ht="11">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3582,7 +3581,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="9">
+    <row r="41" spans="1:16" ht="11">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3632,7 +3631,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="9">
+    <row r="42" spans="1:16" ht="11">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3682,7 +3681,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="9">
+    <row r="43" spans="1:16" ht="11">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3732,7 +3731,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="9">
+    <row r="44" spans="1:16" ht="11">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="9">
+    <row r="45" spans="1:16" ht="11">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3832,7 +3831,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="9">
+    <row r="46" spans="1:16" ht="11">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3882,7 +3881,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="9">
+    <row r="47" spans="1:16" ht="11">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="9">
+    <row r="48" spans="1:16" ht="11">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3982,7 +3981,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="9">
+    <row r="49" spans="1:16" ht="11">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4032,7 +4031,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="9">
+    <row r="50" spans="1:16" ht="11">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4082,7 +4081,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="9">
+    <row r="51" spans="1:16" ht="11">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="9">
+    <row r="52" spans="1:16" ht="11">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="9">
+    <row r="53" spans="1:16" ht="11">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="9">
+    <row r="54" spans="1:16" ht="11">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="9">
+    <row r="55" spans="1:16" ht="11">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4332,7 +4331,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="9">
+    <row r="56" spans="1:16" ht="11">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4382,7 +4381,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="9">
+    <row r="57" spans="1:16" ht="11">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4432,7 +4431,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="9">
+    <row r="58" spans="1:16" ht="11">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4482,7 +4481,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="9">
+    <row r="59" spans="1:16" ht="11">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="9">
+    <row r="60" spans="1:16" ht="11">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4582,7 +4581,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="9">
+    <row r="61" spans="1:16" ht="11">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="9">
+    <row r="62" spans="1:16" ht="11">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4650,7 +4649,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.6" customHeight="1">
+    <row r="63" spans="1:16" ht="39.5" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4722,10 +4721,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6143,10 +6142,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/NC/trans/VSbS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\NC\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07E2BAD2-9210-BD45-949D-DA1A84031847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC5C69F0-D281-4EE7-BA49-B80A5B9AC3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1331,9 +1331,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1371,7 +1371,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1477,7 +1477,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1619,7 +1619,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1628,9 +1628,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.1640625" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1641,7 +1641,7 @@
         <v>25</v>
       </c>
       <c r="C1" s="104">
-        <v>45295</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1754,14 +1754,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="4"/>
+    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1799,7 +1799,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="11">
+    <row r="3" spans="1:16" ht="9">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1841,7 +1841,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="11">
+    <row r="5" spans="1:16" ht="9">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1869,7 +1869,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="11">
+    <row r="6" spans="1:16" ht="9">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="11">
+    <row r="7" spans="1:16" ht="9">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1943,7 +1943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="11">
+    <row r="8" spans="1:16" ht="9">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1991,7 +1991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="11">
+    <row r="9" spans="1:16" ht="9">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2031,7 +2031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="11">
+    <row r="10" spans="1:16" ht="9">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="11">
+    <row r="11" spans="1:16" ht="9">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="11">
+    <row r="12" spans="1:16" ht="9">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="11">
+    <row r="13" spans="1:16" ht="9">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="11">
+    <row r="14" spans="1:16" ht="9">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="11">
+    <row r="15" spans="1:16" ht="9">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="11">
+    <row r="16" spans="1:16" ht="9">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="11">
+    <row r="17" spans="1:16" ht="9">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="11">
+    <row r="18" spans="1:16" ht="9">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="11">
+    <row r="19" spans="1:16" ht="9">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="11">
+    <row r="20" spans="1:16" ht="9">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="11">
+    <row r="21" spans="1:16" ht="9">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="11">
+    <row r="22" spans="1:16" ht="9">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="11">
+    <row r="23" spans="1:16" ht="9">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="11">
+    <row r="24" spans="1:16" ht="9">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="11">
+    <row r="25" spans="1:16" ht="9">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="11">
+    <row r="26" spans="1:16" ht="9">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="11">
+    <row r="27" spans="1:16" ht="9">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="11">
+    <row r="28" spans="1:16" ht="9">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="11">
+    <row r="29" spans="1:16" ht="9">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="11">
+    <row r="30" spans="1:16" ht="9">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="11">
+    <row r="31" spans="1:16" ht="9">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="11">
+    <row r="32" spans="1:16" ht="9">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="11">
+    <row r="33" spans="1:16" ht="9">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="11">
+    <row r="34" spans="1:16" ht="9">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="11">
+    <row r="35" spans="1:16" ht="9">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="11">
+    <row r="36" spans="1:16" ht="9">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="11">
+    <row r="37" spans="1:16" ht="9">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="11">
+    <row r="38" spans="1:16" ht="9">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="11">
+    <row r="39" spans="1:16" ht="9">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="11">
+    <row r="40" spans="1:16" ht="9">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="11">
+    <row r="41" spans="1:16" ht="9">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="11">
+    <row r="42" spans="1:16" ht="9">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="11">
+    <row r="43" spans="1:16" ht="9">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="11">
+    <row r="44" spans="1:16" ht="9">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="11">
+    <row r="45" spans="1:16" ht="9">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="11">
+    <row r="46" spans="1:16" ht="9">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="11">
+    <row r="47" spans="1:16" ht="9">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="11">
+    <row r="48" spans="1:16" ht="9">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="11">
+    <row r="49" spans="1:16" ht="9">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="11">
+    <row r="50" spans="1:16" ht="9">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="11">
+    <row r="51" spans="1:16" ht="9">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="11">
+    <row r="52" spans="1:16" ht="9">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="11">
+    <row r="53" spans="1:16" ht="9">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="11">
+    <row r="54" spans="1:16" ht="9">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="11">
+    <row r="55" spans="1:16" ht="9">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="11">
+    <row r="56" spans="1:16" ht="9">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="11">
+    <row r="57" spans="1:16" ht="9">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="11">
+    <row r="58" spans="1:16" ht="9">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="11">
+    <row r="59" spans="1:16" ht="9">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="11">
+    <row r="60" spans="1:16" ht="9">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="11">
+    <row r="61" spans="1:16" ht="9">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="11">
+    <row r="62" spans="1:16" ht="9">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4649,7 +4649,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.5" customHeight="1">
+    <row r="63" spans="1:16" ht="39.6" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4721,10 +4721,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6142,10 +6142,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
